--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -44716,7 +44716,7 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407494</v>
+        <v>3.492445136407493</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
@@ -44739,7 +44739,7 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611697</v>
+        <v>3.502786823611696</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
@@ -44762,7 +44762,7 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199886</v>
+        <v>3.496848329199885</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
@@ -44785,7 +44785,7 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910629</v>
+        <v>3.499968163910628</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
@@ -44808,7 +44808,7 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078596</v>
+        <v>3.490055666078595</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
@@ -44831,7 +44831,7 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880268</v>
+        <v>3.485875018880267</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
@@ -44854,7 +44854,7 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234393</v>
+        <v>3.480688917234392</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
@@ -44900,7 +44900,7 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767396</v>
+        <v>3.492098065767395</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
@@ -44923,7 +44923,7 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.57367044979254</v>
+        <v>3.573670449792539</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
@@ -44969,7 +44969,7 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410715</v>
+        <v>3.691568158410714</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
@@ -44992,7 +44992,7 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240575</v>
+        <v>3.676837974240574</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
@@ -45015,7 +45015,7 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085278</v>
+        <v>3.685157806085277</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
@@ -45038,7 +45038,7 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.6848402482821</v>
+        <v>3.684840248282099</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
@@ -45061,7 +45061,7 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116216</v>
+        <v>3.710931958116214</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
@@ -45084,7 +45084,7 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081568</v>
+        <v>3.768948099081566</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
@@ -45107,7 +45107,7 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425328</v>
+        <v>3.728574354425326</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
@@ -45130,7 +45130,7 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702413</v>
+        <v>3.747699084702411</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
@@ -45153,16 +45153,16 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.403799345350452</v>
+        <v>3.40379934535045</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.3690969895815616</v>
+        <v>0.3686224325611981</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.311184324062738</v>
+        <v>3.310994501254593</v>
       </c>
       <c r="F1896" t="n">
         <v>1.218320762245822</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.3686224325611981</v>
+        <v>0.3690679478648619</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.310994501254593</v>
+        <v>3.311172707376059</v>
       </c>
       <c r="F1896" t="n">
         <v>1.218320762245822</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-15.9%</t>
+          <t>-19.7%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>66.0%</t>
+          <t>64.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.24</t>
+          <t>-0.30</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>73.2%</t>
+          <t>73.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.7%</t>
+          <t>56.4%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>13.5%</t>
+          <t>12.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-8.9%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>53.7%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.0</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>475.9%</t>
+          <t>471.7%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-124.7%</t>
+          <t>-152.0%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>75.2%</t>
+          <t>71.8%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.7%</t>
+          <t>38.4%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>35.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>10.1%</t>
+          <t>9.9%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>71.7%</t>
+          <t>66.6%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.3%</t>
+          <t>32.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.4%</t>
+          <t>-19.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-45.1%</t>
+          <t>-56.0%</t>
         </is>
       </c>
     </row>
@@ -45159,10 +45159,10 @@
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.3690679478648619</v>
+        <v>0.09560735799941766</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.311172707376059</v>
+        <v>3.201788471429881</v>
       </c>
       <c r="F1896" t="n">
         <v>1.218320762245822</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309425</v>
+        <v>3.311086391309426</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -44417,7 +44417,7 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
@@ -44440,7 +44440,7 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
@@ -44463,7 +44463,7 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
@@ -44486,7 +44486,7 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
@@ -44509,7 +44509,7 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
@@ -44532,7 +44532,7 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
@@ -44555,7 +44555,7 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
@@ -44578,7 +44578,7 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
@@ -44624,7 +44624,7 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
@@ -44670,7 +44670,7 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
@@ -44693,7 +44693,7 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
@@ -45153,7 +45153,7 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.40379934535045</v>
+        <v>3.403799345350451</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -600,26 +600,26 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>52.0%</t>
+          <t>51.8%</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>67.8%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>53.2%</t>
+          <t>53.3%</t>
         </is>
       </c>
       <c r="F2" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -628,17 +628,17 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>68.4%</t>
+          <t>68.7%</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>67.4%</t>
+          <t>67.3%</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -657,7 +657,7 @@
         </is>
       </c>
       <c r="N2" t="n">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
@@ -746,7 +746,7 @@
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>12.3%</t>
+          <t>12.7%</t>
         </is>
       </c>
     </row>
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>76.6%</t>
+          <t>64.2%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>31.5%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.70</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -777,7 +777,7 @@
         </is>
       </c>
       <c r="F3" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -786,12 +786,12 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>29.8%</t>
+          <t>36.7%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>15.5%</t>
+          <t>32.9%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2021-03-21</t>
+          <t>2024-03-04</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2021-03-24</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-11.3%</t>
+          <t>-31.7%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-2.7%</t>
+          <t>-3.5%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-1.8%</t>
+          <t>-2.2%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-5.4%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>63.8%</t>
+          <t>48.4%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>22.7%</t>
+          <t>24.6%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.3</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-5.1%</t>
+          <t>-4.0%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>4.8%</t>
+          <t>-26.7%</t>
         </is>
       </c>
     </row>
@@ -916,26 +916,26 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-19.7%</t>
+          <t>-27.1%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>64.9%</t>
+          <t>67.1%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.30</t>
+          <t>-0.40</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.6%</t>
+          <t>52.5%</t>
         </is>
       </c>
       <c r="F4" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -944,12 +944,12 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>73.1%</t>
+          <t>77.1%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -959,7 +959,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>99.2%</t>
+          <t>99.5%</t>
         </is>
       </c>
       <c r="L4" t="inlineStr">
@@ -973,7 +973,7 @@
         </is>
       </c>
       <c r="N4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O4" t="inlineStr">
         <is>
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.8%</t>
+          <t>11.8%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-8.9%</t>
+          <t>-17.3%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>53.3%</t>
+          <t>55.2%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.3</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>471.7%</t>
+          <t>467.2%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-84.0%</t>
+          <t>-80.8%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-152.0%</t>
+          <t>-191.3%</t>
         </is>
       </c>
     </row>
@@ -1074,26 +1074,26 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>71.8%</t>
+          <t>66.1%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>39.0%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>1.70</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.1%</t>
+          <t>58.0%</t>
         </is>
       </c>
       <c r="F5" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -1102,12 +1102,12 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>42.9%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -1117,7 +1117,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>82.2%</t>
+          <t>85.0%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1131,7 +1131,7 @@
         </is>
       </c>
       <c r="N5" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="O5" t="inlineStr">
         <is>
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.9%</t>
+          <t>9.6%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>66.6%</t>
+          <t>61.1%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>32.5%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.1</t>
+          <t>1.9</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,12 +1185,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.0%</t>
+          <t>-19.2%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.9%</t>
+          <t>38.6%</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-56.0%</t>
+          <t>-71.8%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>13.8%</t>
+          <t>6.4%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>45.3%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.32</t>
+          <t>0.14</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1251,7 +1251,7 @@
         </is>
       </c>
       <c r="F6" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -1260,12 +1260,12 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>41.1%</t>
+          <t>44.1%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>91.1%</t>
+          <t>93.7%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1289,7 +1289,7 @@
         </is>
       </c>
       <c r="N6" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="O6" t="inlineStr">
         <is>
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>7.4%</t>
+          <t>6.7%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>23.2%</t>
+          <t>15.0%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>37.3%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.6</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>3.6%</t>
+          <t>60.3%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-154.9%</t>
+          <t>-155.6%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-102.2%</t>
+          <t>-131.7%</t>
         </is>
       </c>
     </row>
@@ -1390,26 +1390,26 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>96.1%</t>
+          <t>26.4%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>38.4%</t>
+          <t>54.7%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.4%</t>
+          <t>59.3%</t>
         </is>
       </c>
       <c r="F7" t="n">
-        <v>1893</v>
+        <v>1894</v>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>2024-03-07</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>43.5%</t>
+          <t>75.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>74.7%</t>
+          <t>95.0%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-02-06</t>
+          <t>2024-03-08</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>22</v>
+        <v>0</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,57 +1456,57 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-2.8%</t>
+          <t>-4.1%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-0.7%</t>
+          <t>-1.4%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>10.0%</t>
+          <t>9.4%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-14.0%</t>
+          <t>-18.8%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>89.9%</t>
+          <t>20.0%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>32.0%</t>
+          <t>44.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>2.8</t>
+          <t>0.4</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.1</t>
+          <t>0.2</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-14.7%</t>
+          <t>-12.2%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>35.7%</t>
+          <t>35.4%</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-56.5%</t>
+          <t>-161.8%</t>
         </is>
       </c>
     </row>
@@ -1551,7 +1551,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1896"/>
+  <dimension ref="A1:G1897"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -44371,7 +44371,7 @@
         <v>45324</v>
       </c>
       <c r="B1862" t="n">
-        <v>3.311086391309426</v>
+        <v>3.311086391309425</v>
       </c>
       <c r="C1862" t="n">
         <v>3.117424460923081</v>
@@ -44394,22 +44394,22 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-2.359543798222353</v>
+        <v>-2.75278660390213</v>
       </c>
       <c r="E1863" t="n">
-        <v>2.172505032326224</v>
+        <v>2.015207910054313</v>
       </c>
       <c r="F1863" t="n">
-        <v>0.1718970014009391</v>
+        <v>-0.1234192628351061</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.219817176769476</v>
+        <v>3.042627418227849</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330524</v>
+        <v>3.300815818330523</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-2.360835819996692</v>
+        <v>-2.754078625676468</v>
       </c>
       <c r="E1864" t="n">
-        <v>2.170749767631248</v>
+        <v>2.013452645359337</v>
       </c>
       <c r="F1864" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.217803507719633</v>
+        <v>3.040613749178005</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.30261819419174</v>
+        <v>3.302618194191739</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-2.365650412251533</v>
+        <v>-2.758893217931309</v>
       </c>
       <c r="E1865" t="n">
-        <v>2.164009363200772</v>
+        <v>2.006712240928861</v>
       </c>
       <c r="F1865" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1865" t="n">
-        <v>3.212988940191093</v>
+        <v>3.035799181649466</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108642</v>
+        <v>3.305023265108641</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-2.362493711221329</v>
+        <v>-2.755736516901106</v>
       </c>
       <c r="E1866" t="n">
-        <v>2.163266094221731</v>
+        <v>2.00596897194982</v>
       </c>
       <c r="F1866" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.210982990799971</v>
+        <v>3.033793232258343</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097824</v>
+        <v>3.341378723097823</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-2.366506743633851</v>
+        <v>-2.759749549313627</v>
       </c>
       <c r="E1867" t="n">
-        <v>2.171919571925401</v>
+        <v>2.014622449653491</v>
       </c>
       <c r="F1867" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1867" t="n">
-        <v>3.22124168146865</v>
+        <v>3.044051922927022</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094119</v>
+        <v>3.374439043094118</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-2.380221607958963</v>
+        <v>-2.773464413638739</v>
       </c>
       <c r="E1868" t="n">
-        <v>2.162533191341051</v>
+        <v>2.005236069069141</v>
       </c>
       <c r="F1868" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1868" t="n">
-        <v>3.217341246614345</v>
+        <v>3.040151488072718</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199289</v>
+        <v>3.405960511199288</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-2.385738527802929</v>
+        <v>-2.778981333482705</v>
       </c>
       <c r="E1869" t="n">
-        <v>2.158731343458466</v>
+        <v>2.001434221186555</v>
       </c>
       <c r="F1869" t="n">
-        <v>0.170604979626601</v>
+        <v>-0.1247112846094442</v>
       </c>
       <c r="G1869" t="n">
-        <v>3.215746166669346</v>
+        <v>3.038556408127719</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969598</v>
+        <v>3.424633354969597</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-2.390551566268266</v>
+        <v>-2.783794371948042</v>
       </c>
       <c r="E1870" t="n">
-        <v>2.160585104001539</v>
+        <v>2.003287981729629</v>
       </c>
       <c r="F1870" t="n">
-        <v>0.1690583449238152</v>
+        <v>-0.12625791931223</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.218597161776882</v>
+        <v>3.041407403235255</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.419979433923091</v>
+        <v>3.41997943392309</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-2.388434407543973</v>
+        <v>-2.781677213223749</v>
       </c>
       <c r="E1871" t="n">
-        <v>2.157405662956853</v>
+        <v>2.000108540684943</v>
       </c>
       <c r="F1871" t="n">
-        <v>0.1690583449238152</v>
+        <v>-0.12625791931223</v>
       </c>
       <c r="G1871" t="n">
-        <v>3.214570857242479</v>
+        <v>3.037381098700852</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-2.387957060965483</v>
+        <v>-2.781199866645259</v>
       </c>
       <c r="E1872" t="n">
-        <v>2.157494500266665</v>
+        <v>2.000197377994755</v>
       </c>
       <c r="F1872" t="n">
-        <v>0.1690583449238152</v>
+        <v>-0.12625791931223</v>
       </c>
       <c r="G1872" t="n">
-        <v>3.214468755920895</v>
+        <v>3.037278997379268</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317619</v>
+        <v>3.447750501317618</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-2.386932274658625</v>
+        <v>-2.780175080338402</v>
       </c>
       <c r="E1873" t="n">
-        <v>2.160475930760838</v>
+        <v>2.003178808488928</v>
       </c>
       <c r="F1873" t="n">
-        <v>0.1700831312306728</v>
+        <v>-0.1252331330053724</v>
       </c>
       <c r="G1873" t="n">
-        <v>3.21765514367644</v>
+        <v>3.040465385134813</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-2.405673654917544</v>
+        <v>-2.79891646059732</v>
       </c>
       <c r="E1874" t="n">
-        <v>2.158329681955321</v>
+        <v>2.001032559683411</v>
       </c>
       <c r="F1874" t="n">
-        <v>0.1700831312306728</v>
+        <v>-0.1252331330053724</v>
       </c>
       <c r="G1874" t="n">
-        <v>3.22300544697449</v>
+        <v>3.045815688432863</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341315</v>
+        <v>3.503170282341314</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-2.418642997702642</v>
+        <v>-2.811885803382419</v>
       </c>
       <c r="E1875" t="n">
-        <v>2.161057964798459</v>
+        <v>2.003760842526549</v>
       </c>
       <c r="F1875" t="n">
-        <v>0.1571137884455743</v>
+        <v>-0.138202475790471</v>
       </c>
       <c r="G1875" t="n">
-        <v>3.223139861260608</v>
+        <v>3.045950102718981</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776678</v>
+        <v>3.500446096776677</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-2.412166850909083</v>
+        <v>-2.805409656588859</v>
       </c>
       <c r="E1876" t="n">
-        <v>2.166690174137652</v>
+        <v>2.009393051865741</v>
       </c>
       <c r="F1876" t="n">
-        <v>0.1635899352391338</v>
+        <v>-0.1317263289969114</v>
       </c>
       <c r="G1876" t="n">
-        <v>3.230067299958513</v>
+        <v>3.052877541416886</v>
       </c>
     </row>
     <row r="1877">
@@ -44722,16 +44722,16 @@
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-2.408475925952672</v>
+        <v>-2.801718731632448</v>
       </c>
       <c r="E1877" t="n">
-        <v>2.168166544120216</v>
+        <v>2.010869421848306</v>
       </c>
       <c r="F1877" t="n">
-        <v>0.1635899352391338</v>
+        <v>-0.1317263289969114</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.230067299958513</v>
+        <v>3.052877541416886</v>
       </c>
     </row>
     <row r="1878">
@@ -44745,16 +44745,16 @@
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-2.401260573080856</v>
+        <v>-2.794503378760632</v>
       </c>
       <c r="E1878" t="n">
-        <v>2.176565882387585</v>
+        <v>2.019268760115675</v>
       </c>
       <c r="F1878" t="n">
-        <v>0.2333681705295157</v>
+        <v>-0.06194809370652954</v>
       </c>
       <c r="G1878" t="n">
-        <v>3.277447438251385</v>
+        <v>3.100257679709757</v>
       </c>
     </row>
     <row r="1879">
@@ -44768,16 +44768,16 @@
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-2.35023272699903</v>
+        <v>-2.743475532678806</v>
       </c>
       <c r="E1879" t="n">
-        <v>2.201459575304751</v>
+        <v>2.044162453032841</v>
       </c>
       <c r="F1879" t="n">
-        <v>0.3085775088366167</v>
+        <v>0.01326124460057143</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.327055595720081</v>
+        <v>3.149865837178454</v>
       </c>
     </row>
     <row r="1880">
@@ -44791,16 +44791,16 @@
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-2.276762895331581</v>
+        <v>-2.670005701011358</v>
       </c>
       <c r="E1880" t="n">
-        <v>2.246219209465152</v>
+        <v>2.088922087193241</v>
       </c>
       <c r="F1880" t="n">
-        <v>0.3820473405040651</v>
+        <v>0.08673107626801985</v>
       </c>
       <c r="G1880" t="n">
-        <v>3.386509196213972</v>
+        <v>3.209319437672344</v>
       </c>
     </row>
     <row r="1881">
@@ -44814,16 +44814,16 @@
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-2.196390539867652</v>
+        <v>-2.589633345547428</v>
       </c>
       <c r="E1881" t="n">
-        <v>2.292923372398241</v>
+        <v>2.13562625012633</v>
       </c>
       <c r="F1881" t="n">
-        <v>0.4624196959679947</v>
+        <v>0.1671034317319495</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.449287830239846</v>
+        <v>3.272098071698219</v>
       </c>
     </row>
     <row r="1882">
@@ -44837,16 +44837,16 @@
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-2.163458670054801</v>
+        <v>-2.556701475734577</v>
       </c>
       <c r="E1882" t="n">
-        <v>2.298876955421785</v>
+        <v>2.141579833149875</v>
       </c>
       <c r="F1882" t="n">
-        <v>0.4624196959679947</v>
+        <v>0.1671034317319495</v>
       </c>
       <c r="G1882" t="n">
-        <v>3.44206866533825</v>
+        <v>3.264878906796623</v>
       </c>
     </row>
     <row r="1883">
@@ -44860,16 +44860,16 @@
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-2.183623311604349</v>
+        <v>-2.576866117284125</v>
       </c>
       <c r="E1883" t="n">
-        <v>2.28413890802799</v>
+        <v>2.12684178575608</v>
       </c>
       <c r="F1883" t="n">
-        <v>0.4422550544184474</v>
+        <v>0.1469387901824021</v>
       </c>
       <c r="G1883" t="n">
-        <v>3.423297689634545</v>
+        <v>3.246107931092918</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-2.124956381582816</v>
+        <v>-2.518199187262592</v>
       </c>
       <c r="E1884" t="n">
-        <v>2.308721469875159</v>
+        <v>2.151424347603249</v>
       </c>
       <c r="F1884" t="n">
-        <v>0.5272145228485851</v>
+        <v>0.2318982586125398</v>
       </c>
       <c r="G1884" t="n">
-        <v>3.475389160531184</v>
+        <v>3.298199401989557</v>
       </c>
     </row>
     <row r="1885">
@@ -44906,16 +44906,16 @@
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-2.061887149276476</v>
+        <v>-2.455129954956252</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.33664289142681</v>
+        <v>2.179345769154899</v>
       </c>
       <c r="F1885" t="n">
-        <v>0.4987009601663506</v>
+        <v>0.2033846959303053</v>
       </c>
       <c r="G1885" t="n">
-        <v>3.460974751550958</v>
+        <v>3.283784993009331</v>
       </c>
     </row>
     <row r="1886">
@@ -44929,16 +44929,16 @@
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-2.009871635307663</v>
+        <v>-2.403114440987439</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.361439432700736</v>
+        <v>2.204142310428825</v>
       </c>
       <c r="F1886" t="n">
-        <v>0.4987009601663506</v>
+        <v>0.2033846959303053</v>
       </c>
       <c r="G1886" t="n">
-        <v>3.464965087237359</v>
+        <v>3.287775328695732</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-1.834301966386759</v>
+        <v>-2.227544772066536</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.430192073370355</v>
+        <v>2.272894951098445</v>
       </c>
       <c r="F1887" t="n">
-        <v>0.4987009601663506</v>
+        <v>0.2033846959303053</v>
       </c>
       <c r="G1887" t="n">
-        <v>3.463489860338617</v>
+        <v>3.28630010179699</v>
       </c>
     </row>
     <row r="1888">
@@ -44975,16 +44975,16 @@
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-1.637032560658761</v>
+        <v>-2.030275366338537</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.524153245826427</v>
+        <v>2.366856123554517</v>
       </c>
       <c r="F1888" t="n">
-        <v>0.6959703658943487</v>
+        <v>0.4006541016583035</v>
       </c>
       <c r="G1888" t="n">
-        <v>3.596904913940288</v>
+        <v>3.419715155398661</v>
       </c>
     </row>
     <row r="1889">
@@ -44998,16 +44998,16 @@
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-1.437880453421662</v>
+        <v>-1.831123259101438</v>
       </c>
       <c r="E1889" t="n">
-        <v>2.590762955074584</v>
+        <v>2.433465832802673</v>
       </c>
       <c r="F1889" t="n">
-        <v>0.861292891844162</v>
+        <v>0.5659766276081168</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.683047295863493</v>
+        <v>3.505857537321866</v>
       </c>
     </row>
     <row r="1890">
@@ -45021,16 +45021,16 @@
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-1.212035300702251</v>
+        <v>-1.605278106382027</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.690680089198557</v>
+        <v>2.533382966926646</v>
       </c>
       <c r="F1890" t="n">
-        <v>0.9032195674313257</v>
+        <v>0.6079033031952805</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.717782374252</v>
+        <v>3.540592615710373</v>
       </c>
     </row>
     <row r="1891">
@@ -45044,16 +45044,16 @@
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-0.9257604883795567</v>
+        <v>-1.319003294059333</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.806329158683694</v>
+        <v>2.649032036411783</v>
       </c>
       <c r="F1891" t="n">
-        <v>0.9032195674313257</v>
+        <v>0.6079033031952805</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.718921518808059</v>
+        <v>3.541731760266432</v>
       </c>
     </row>
     <row r="1892">
@@ -45067,16 +45067,16 @@
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-0.6989646613062228</v>
+        <v>-1.092207466985999</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.899681263675135</v>
+        <v>2.742384141403224</v>
       </c>
       <c r="F1892" t="n">
-        <v>0.9713335120528702</v>
+        <v>0.676017247816825</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.762423659743094</v>
+        <v>3.585233901201466</v>
       </c>
     </row>
     <row r="1893">
@@ -45090,16 +45090,16 @@
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-0.4150559303774739</v>
+        <v>-0.80829873605725</v>
       </c>
       <c r="E1893" t="n">
-        <v>3.018978460285271</v>
+        <v>2.86168133801336</v>
       </c>
       <c r="F1893" t="n">
-        <v>0.9713335120528702</v>
+        <v>0.676017247816825</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.76815736398173</v>
+        <v>3.590967605440103</v>
       </c>
     </row>
     <row r="1894">
@@ -45113,16 +45113,16 @@
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-0.1680686801845218</v>
+        <v>-0.5613114858642979</v>
       </c>
       <c r="E1894" t="n">
-        <v>3.108036097968586</v>
+        <v>2.950738975696676</v>
       </c>
       <c r="F1894" t="n">
-        <v>1.218320762245822</v>
+        <v>0.9230044980097771</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.906612451703636</v>
+        <v>3.729422693162009</v>
       </c>
     </row>
     <row r="1895">
@@ -45136,16 +45136,16 @@
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>0.09576818701954726</v>
+        <v>-0.2974746186602288</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.203687363537306</v>
+        <v>3.046390241265396</v>
       </c>
       <c r="F1895" t="n">
-        <v>1.218320762245822</v>
+        <v>0.9230044980097771</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.896728970390729</v>
+        <v>3.719539211849102</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,45 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.403799345350451</v>
+        <v>3.766313503906228</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>0.09560735799941766</v>
+        <v>-0.2976354476803584</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.201788471429881</v>
+        <v>3.04449134915797</v>
       </c>
       <c r="F1896" t="n">
-        <v>1.218320762245822</v>
+        <v>0.9230044980097771</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.894894409891355</v>
+        <v>3.717704651349728</v>
+      </c>
+    </row>
+    <row r="1897">
+      <c r="A1897" s="2" t="n">
+        <v>45359</v>
+      </c>
+      <c r="B1897" t="n">
+        <v>3.40760767729903</v>
+      </c>
+      <c r="C1897" t="n">
+        <v>2.849409515865033</v>
+      </c>
+      <c r="D1897" t="n">
+        <v>-0.2976354476803584</v>
+      </c>
+      <c r="E1897" t="n">
+        <v>3.04449134915797</v>
+      </c>
+      <c r="F1897" t="n">
+        <v>0.9230044980097771</v>
+      </c>
+      <c r="G1897" t="n">
+        <v>2.842473312851401</v>
       </c>
     </row>
   </sheetData>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -916,22 +916,22 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-27.1%</t>
+          <t>-23.4%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>67.1%</t>
+          <t>67.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.40</t>
+          <t>-0.34</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>52.5%</t>
+          <t>52.6%</t>
         </is>
       </c>
       <c r="F4" t="n">
@@ -949,12 +949,12 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>77.1%</t>
+          <t>76.9%</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>56.4%</t>
+          <t>58.6%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>11.8%</t>
+          <t>12.5%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-17.3%</t>
+          <t>-13.2%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>55.2%</t>
+          <t>55.9%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.3</t>
+          <t>-0.2</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,12 +1027,12 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>467.2%</t>
+          <t>469.9%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>-80.8%</t>
+          <t>-80.9%</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-191.3%</t>
+          <t>-163.3%</t>
         </is>
       </c>
     </row>
@@ -1074,22 +1074,22 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>66.1%</t>
+          <t>69.6%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.0%</t>
+          <t>39.2%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.70</t>
+          <t>1.77</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>58.0%</t>
+          <t>58.1%</t>
         </is>
       </c>
       <c r="F5" t="n">
@@ -1112,12 +1112,12 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.0%</t>
+          <t>35.5%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>85.0%</t>
+          <t>84.9%</t>
         </is>
       </c>
       <c r="L5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.6%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>61.1%</t>
+          <t>64.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.5%</t>
+          <t>32.7%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>1.9</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.2%</t>
+          <t>-19.6%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-71.8%</t>
+          <t>-60.6%</t>
         </is>
       </c>
     </row>
@@ -1232,17 +1232,17 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.4%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45.3%</t>
+          <t>45.1%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.14</t>
+          <t>0.15</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -1265,7 +1265,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>44.1%</t>
+          <t>43.7%</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1275,7 +1275,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>93.7%</t>
+          <t>93.6%</t>
         </is>
       </c>
       <c r="L6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.7%</t>
+          <t>6.8%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,12 +1323,12 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>15.0%</t>
+          <t>15.6%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.3%</t>
+          <t>37.2%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
@@ -1343,12 +1343,12 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>60.3%</t>
+          <t>80.2%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>-155.6%</t>
+          <t>-157.5%</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-131.7%</t>
+          <t>-129.8%</t>
         </is>
       </c>
     </row>
@@ -1390,17 +1390,17 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>26.4%</t>
+          <t>24.5%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>54.7%</t>
+          <t>55.0%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>0.45</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -1423,7 +1423,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.0%</t>
+          <t>75.5%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1433,7 +1433,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.0%</t>
+          <t>95.4%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1466,12 +1466,12 @@
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.4%</t>
+          <t>9.5%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.8%</t>
+          <t>-18.9%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
@@ -1481,12 +1481,12 @@
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>20.0%</t>
+          <t>18.8%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.6%</t>
+          <t>44.9%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.2%</t>
+          <t>-12.1%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -44400,16 +44400,16 @@
         <v>3.116678975928913</v>
       </c>
       <c r="D1863" t="n">
-        <v>-2.75278660390213</v>
+        <v>-2.740050208954725</v>
       </c>
       <c r="E1863" t="n">
-        <v>2.015207910054313</v>
+        <v>2.020302468033275</v>
       </c>
       <c r="F1863" t="n">
-        <v>-0.1234192628351061</v>
+        <v>-0.10474211879816</v>
       </c>
       <c r="G1863" t="n">
-        <v>3.042627418227849</v>
+        <v>3.053833704650017</v>
       </c>
     </row>
     <row r="1864">
@@ -44417,22 +44417,22 @@
         <v>45326</v>
       </c>
       <c r="B1864" t="n">
-        <v>3.300815818330523</v>
+        <v>3.300815818330524</v>
       </c>
       <c r="C1864" t="n">
         <v>3.115440519943672</v>
       </c>
       <c r="D1864" t="n">
-        <v>-2.754078625676468</v>
+        <v>-2.741342230729063</v>
       </c>
       <c r="E1864" t="n">
-        <v>2.013452645359337</v>
+        <v>2.018547203338299</v>
       </c>
       <c r="F1864" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1864" t="n">
-        <v>3.040613749178005</v>
+        <v>3.051820035600173</v>
       </c>
     </row>
     <row r="1865">
@@ -44440,22 +44440,22 @@
         <v>45327</v>
       </c>
       <c r="B1865" t="n">
-        <v>3.302618194191739</v>
+        <v>3.30261819419174</v>
       </c>
       <c r="C1865" t="n">
         <v>3.110625952415132</v>
       </c>
       <c r="D1865" t="n">
-        <v>-2.758893217931309</v>
+        <v>-2.746156822983905</v>
       </c>
       <c r="E1865" t="n">
-        <v>2.006712240928861</v>
+        <v>2.011806798907823</v>
       </c>
       <c r="F1865" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1865" t="n">
-        <v>3.035799181649466</v>
+        <v>3.047005468071634</v>
       </c>
     </row>
     <row r="1866">
@@ -44463,22 +44463,22 @@
         <v>45328</v>
       </c>
       <c r="B1866" t="n">
-        <v>3.305023265108641</v>
+        <v>3.305023265108642</v>
       </c>
       <c r="C1866" t="n">
         <v>3.10862000302401</v>
       </c>
       <c r="D1866" t="n">
-        <v>-2.755736516901106</v>
+        <v>-2.743000121953701</v>
       </c>
       <c r="E1866" t="n">
-        <v>2.00596897194982</v>
+        <v>2.011063529928782</v>
       </c>
       <c r="F1866" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1866" t="n">
-        <v>3.033793232258343</v>
+        <v>3.044999518680511</v>
       </c>
     </row>
     <row r="1867">
@@ -44486,22 +44486,22 @@
         <v>45329</v>
       </c>
       <c r="B1867" t="n">
-        <v>3.341378723097823</v>
+        <v>3.341378723097824</v>
       </c>
       <c r="C1867" t="n">
         <v>3.118878693692689</v>
       </c>
       <c r="D1867" t="n">
-        <v>-2.759749549313627</v>
+        <v>-2.747013154366222</v>
       </c>
       <c r="E1867" t="n">
-        <v>2.014622449653491</v>
+        <v>2.019717007632452</v>
       </c>
       <c r="F1867" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1867" t="n">
-        <v>3.044051922927022</v>
+        <v>3.05525820934919</v>
       </c>
     </row>
     <row r="1868">
@@ -44509,22 +44509,22 @@
         <v>45330</v>
       </c>
       <c r="B1868" t="n">
-        <v>3.374439043094118</v>
+        <v>3.374439043094119</v>
       </c>
       <c r="C1868" t="n">
         <v>3.114978258838384</v>
       </c>
       <c r="D1868" t="n">
-        <v>-2.773464413638739</v>
+        <v>-2.760728018691334</v>
       </c>
       <c r="E1868" t="n">
-        <v>2.005236069069141</v>
+        <v>2.010330627048103</v>
       </c>
       <c r="F1868" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1868" t="n">
-        <v>3.040151488072718</v>
+        <v>3.051357774494885</v>
       </c>
     </row>
     <row r="1869">
@@ -44532,22 +44532,22 @@
         <v>45331</v>
       </c>
       <c r="B1869" t="n">
-        <v>3.405960511199288</v>
+        <v>3.405960511199289</v>
       </c>
       <c r="C1869" t="n">
         <v>3.113383178893385</v>
       </c>
       <c r="D1869" t="n">
-        <v>-2.778981333482705</v>
+        <v>-2.766244938535301</v>
       </c>
       <c r="E1869" t="n">
-        <v>2.001434221186555</v>
+        <v>2.006528779165517</v>
       </c>
       <c r="F1869" t="n">
-        <v>-0.1247112846094442</v>
+        <v>-0.1060341405724981</v>
       </c>
       <c r="G1869" t="n">
-        <v>3.038556408127719</v>
+        <v>3.049762694549886</v>
       </c>
     </row>
     <row r="1870">
@@ -44555,22 +44555,22 @@
         <v>45332</v>
       </c>
       <c r="B1870" t="n">
-        <v>3.424633354969597</v>
+        <v>3.424633354969598</v>
       </c>
       <c r="C1870" t="n">
         <v>3.117162154822593</v>
       </c>
       <c r="D1870" t="n">
-        <v>-2.783794371948042</v>
+        <v>-2.771057977000637</v>
       </c>
       <c r="E1870" t="n">
-        <v>2.003287981729629</v>
+        <v>2.008382539708591</v>
       </c>
       <c r="F1870" t="n">
-        <v>-0.12625791931223</v>
+        <v>-0.1075807752752839</v>
       </c>
       <c r="G1870" t="n">
-        <v>3.041407403235255</v>
+        <v>3.052613689657423</v>
       </c>
     </row>
     <row r="1871">
@@ -44578,22 +44578,22 @@
         <v>45333</v>
       </c>
       <c r="B1871" t="n">
-        <v>3.41997943392309</v>
+        <v>3.419979433923091</v>
       </c>
       <c r="C1871" t="n">
         <v>3.11313585028819</v>
       </c>
       <c r="D1871" t="n">
-        <v>-2.781677213223749</v>
+        <v>-2.768940818276344</v>
       </c>
       <c r="E1871" t="n">
-        <v>2.000108540684943</v>
+        <v>2.005203098663904</v>
       </c>
       <c r="F1871" t="n">
-        <v>-0.12625791931223</v>
+        <v>-0.1075807752752839</v>
       </c>
       <c r="G1871" t="n">
-        <v>3.037381098700852</v>
+        <v>3.04858738512302</v>
       </c>
     </row>
     <row r="1872">
@@ -44607,16 +44607,16 @@
         <v>3.113033748966606</v>
       </c>
       <c r="D1872" t="n">
-        <v>-2.781199866645259</v>
+        <v>-2.768463471697854</v>
       </c>
       <c r="E1872" t="n">
-        <v>2.000197377994755</v>
+        <v>2.005291935973717</v>
       </c>
       <c r="F1872" t="n">
-        <v>-0.12625791931223</v>
+        <v>-0.1075807752752839</v>
       </c>
       <c r="G1872" t="n">
-        <v>3.037278997379268</v>
+        <v>3.048485283801436</v>
       </c>
     </row>
     <row r="1873">
@@ -44624,22 +44624,22 @@
         <v>45335</v>
       </c>
       <c r="B1873" t="n">
-        <v>3.447750501317618</v>
+        <v>3.447750501317619</v>
       </c>
       <c r="C1873" t="n">
         <v>3.115605264938036</v>
       </c>
       <c r="D1873" t="n">
-        <v>-2.780175080338402</v>
+        <v>-2.767438685390997</v>
       </c>
       <c r="E1873" t="n">
-        <v>2.003178808488928</v>
+        <v>2.00827336646789</v>
       </c>
       <c r="F1873" t="n">
-        <v>-0.1252331330053724</v>
+        <v>-0.1065559889684263</v>
       </c>
       <c r="G1873" t="n">
-        <v>3.040465385134813</v>
+        <v>3.05167167155698</v>
       </c>
     </row>
     <row r="1874">
@@ -44653,16 +44653,16 @@
         <v>3.120955568236086</v>
       </c>
       <c r="D1874" t="n">
-        <v>-2.79891646059732</v>
+        <v>-2.786180065649915</v>
       </c>
       <c r="E1874" t="n">
-        <v>2.001032559683411</v>
+        <v>2.006127117662373</v>
       </c>
       <c r="F1874" t="n">
-        <v>-0.1252331330053724</v>
+        <v>-0.1065559889684263</v>
       </c>
       <c r="G1874" t="n">
-        <v>3.045815688432863</v>
+        <v>3.057021974855031</v>
       </c>
     </row>
     <row r="1875">
@@ -44670,22 +44670,22 @@
         <v>45337</v>
       </c>
       <c r="B1875" t="n">
-        <v>3.503170282341314</v>
+        <v>3.503170282341315</v>
       </c>
       <c r="C1875" t="n">
         <v>3.128871588193264</v>
       </c>
       <c r="D1875" t="n">
-        <v>-2.811885803382419</v>
+        <v>-2.799149408435014</v>
       </c>
       <c r="E1875" t="n">
-        <v>2.003760842526549</v>
+        <v>2.008855400505511</v>
       </c>
       <c r="F1875" t="n">
-        <v>-0.138202475790471</v>
+        <v>-0.1195253317535249</v>
       </c>
       <c r="G1875" t="n">
-        <v>3.045950102718981</v>
+        <v>3.057156389141149</v>
       </c>
     </row>
     <row r="1876">
@@ -44693,22 +44693,22 @@
         <v>45338</v>
       </c>
       <c r="B1876" t="n">
-        <v>3.500446096776677</v>
+        <v>3.500446096776678</v>
       </c>
       <c r="C1876" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1876" t="n">
-        <v>-2.805409656588859</v>
+        <v>-2.792673261641454</v>
       </c>
       <c r="E1876" t="n">
-        <v>2.009393051865741</v>
+        <v>2.014487609844704</v>
       </c>
       <c r="F1876" t="n">
-        <v>-0.1317263289969114</v>
+        <v>-0.1130491849599653</v>
       </c>
       <c r="G1876" t="n">
-        <v>3.052877541416886</v>
+        <v>3.064083827839053</v>
       </c>
     </row>
     <row r="1877">
@@ -44716,22 +44716,22 @@
         <v>45339</v>
       </c>
       <c r="B1877" t="n">
-        <v>3.492445136407493</v>
+        <v>3.492445136407494</v>
       </c>
       <c r="C1877" t="n">
         <v>3.131913338815032</v>
       </c>
       <c r="D1877" t="n">
-        <v>-2.801718731632448</v>
+        <v>-2.788982336685043</v>
       </c>
       <c r="E1877" t="n">
-        <v>2.010869421848306</v>
+        <v>2.015963979827268</v>
       </c>
       <c r="F1877" t="n">
-        <v>-0.1317263289969114</v>
+        <v>-0.1130491849599653</v>
       </c>
       <c r="G1877" t="n">
-        <v>3.052877541416886</v>
+        <v>3.064083827839053</v>
       </c>
     </row>
     <row r="1878">
@@ -44739,22 +44739,22 @@
         <v>45340</v>
       </c>
       <c r="B1878" t="n">
-        <v>3.502786823611696</v>
+        <v>3.502786823611697</v>
       </c>
       <c r="C1878" t="n">
         <v>3.137426535933675</v>
       </c>
       <c r="D1878" t="n">
-        <v>-2.794503378760632</v>
+        <v>-2.781766983813227</v>
       </c>
       <c r="E1878" t="n">
-        <v>2.019268760115675</v>
+        <v>2.024363318094637</v>
       </c>
       <c r="F1878" t="n">
-        <v>-0.06194809370652954</v>
+        <v>-0.04327094966958345</v>
       </c>
       <c r="G1878" t="n">
-        <v>3.100257679709757</v>
+        <v>3.111463966131925</v>
       </c>
     </row>
     <row r="1879">
@@ -44762,22 +44762,22 @@
         <v>45341</v>
       </c>
       <c r="B1879" t="n">
-        <v>3.496848329199885</v>
+        <v>3.496848329199886</v>
       </c>
       <c r="C1879" t="n">
         <v>3.141909090418111</v>
       </c>
       <c r="D1879" t="n">
-        <v>-2.743475532678806</v>
+        <v>-2.730739137731401</v>
       </c>
       <c r="E1879" t="n">
-        <v>2.044162453032841</v>
+        <v>2.049257011011803</v>
       </c>
       <c r="F1879" t="n">
-        <v>0.01326124460057143</v>
+        <v>0.03193838863751752</v>
       </c>
       <c r="G1879" t="n">
-        <v>3.149865837178454</v>
+        <v>3.161072123600622</v>
       </c>
     </row>
     <row r="1880">
@@ -44785,22 +44785,22 @@
         <v>45342</v>
       </c>
       <c r="B1880" t="n">
-        <v>3.499968163910628</v>
+        <v>3.499968163910629</v>
       </c>
       <c r="C1880" t="n">
         <v>3.157280791911532</v>
       </c>
       <c r="D1880" t="n">
-        <v>-2.670005701011358</v>
+        <v>-2.657269306063953</v>
       </c>
       <c r="E1880" t="n">
-        <v>2.088922087193241</v>
+        <v>2.094016645172204</v>
       </c>
       <c r="F1880" t="n">
-        <v>0.08673107626801985</v>
+        <v>0.1054082203049659</v>
       </c>
       <c r="G1880" t="n">
-        <v>3.209319437672344</v>
+        <v>3.220525724094512</v>
       </c>
     </row>
     <row r="1881">
@@ -44808,22 +44808,22 @@
         <v>45343</v>
       </c>
       <c r="B1881" t="n">
-        <v>3.490055666078595</v>
+        <v>3.490055666078596</v>
       </c>
       <c r="C1881" t="n">
         <v>3.171836012659049</v>
       </c>
       <c r="D1881" t="n">
-        <v>-2.589633345547428</v>
+        <v>-2.576896950600023</v>
       </c>
       <c r="E1881" t="n">
-        <v>2.13562625012633</v>
+        <v>2.140720808105292</v>
       </c>
       <c r="F1881" t="n">
-        <v>0.1671034317319495</v>
+        <v>0.1857805757688956</v>
       </c>
       <c r="G1881" t="n">
-        <v>3.272098071698219</v>
+        <v>3.283304358120386</v>
       </c>
     </row>
     <row r="1882">
@@ -44831,22 +44831,22 @@
         <v>45344</v>
       </c>
       <c r="B1882" t="n">
-        <v>3.485875018880267</v>
+        <v>3.485875018880268</v>
       </c>
       <c r="C1882" t="n">
         <v>3.164616847757453</v>
       </c>
       <c r="D1882" t="n">
-        <v>-2.556701475734577</v>
+        <v>-2.543965080787173</v>
       </c>
       <c r="E1882" t="n">
-        <v>2.141579833149875</v>
+        <v>2.146674391128836</v>
       </c>
       <c r="F1882" t="n">
-        <v>0.1671034317319495</v>
+        <v>0.1857805757688956</v>
       </c>
       <c r="G1882" t="n">
-        <v>3.264878906796623</v>
+        <v>3.27608519321879</v>
       </c>
     </row>
     <row r="1883">
@@ -44854,22 +44854,22 @@
         <v>45345</v>
       </c>
       <c r="B1883" t="n">
-        <v>3.480688917234392</v>
+        <v>3.480688917234393</v>
       </c>
       <c r="C1883" t="n">
         <v>3.157944656983477</v>
       </c>
       <c r="D1883" t="n">
-        <v>-2.576866117284125</v>
+        <v>-2.56412972233672</v>
       </c>
       <c r="E1883" t="n">
-        <v>2.12684178575608</v>
+        <v>2.131936343735041</v>
       </c>
       <c r="F1883" t="n">
-        <v>0.1469387901824021</v>
+        <v>0.1656159342193482</v>
       </c>
       <c r="G1883" t="n">
-        <v>3.246107931092918</v>
+        <v>3.257314217515086</v>
       </c>
     </row>
     <row r="1884">
@@ -44883,16 +44883,16 @@
         <v>3.159060446822033</v>
       </c>
       <c r="D1884" t="n">
-        <v>-2.518199187262592</v>
+        <v>-2.505462792315187</v>
       </c>
       <c r="E1884" t="n">
-        <v>2.151424347603249</v>
+        <v>2.156518905582211</v>
       </c>
       <c r="F1884" t="n">
-        <v>0.2318982586125398</v>
+        <v>0.2505754026494859</v>
       </c>
       <c r="G1884" t="n">
-        <v>3.298199401989557</v>
+        <v>3.309405688411725</v>
       </c>
     </row>
     <row r="1885">
@@ -44900,22 +44900,22 @@
         <v>45347</v>
       </c>
       <c r="B1885" t="n">
-        <v>3.492098065767395</v>
+        <v>3.492098065767396</v>
       </c>
       <c r="C1885" t="n">
         <v>3.161754175451148</v>
       </c>
       <c r="D1885" t="n">
-        <v>-2.455129954956252</v>
+        <v>-2.442393560008847</v>
       </c>
       <c r="E1885" t="n">
-        <v>2.179345769154899</v>
+        <v>2.184440327133861</v>
       </c>
       <c r="F1885" t="n">
-        <v>0.2033846959303053</v>
+        <v>0.2220618399672514</v>
       </c>
       <c r="G1885" t="n">
-        <v>3.283784993009331</v>
+        <v>3.294991279431499</v>
       </c>
     </row>
     <row r="1886">
@@ -44923,22 +44923,22 @@
         <v>45348</v>
       </c>
       <c r="B1886" t="n">
-        <v>3.573670449792539</v>
+        <v>3.57367044979254</v>
       </c>
       <c r="C1886" t="n">
         <v>3.165744511137548</v>
       </c>
       <c r="D1886" t="n">
-        <v>-2.403114440987439</v>
+        <v>-2.390378046040035</v>
       </c>
       <c r="E1886" t="n">
-        <v>2.204142310428825</v>
+        <v>2.209236868407787</v>
       </c>
       <c r="F1886" t="n">
-        <v>0.2033846959303053</v>
+        <v>0.2220618399672514</v>
       </c>
       <c r="G1886" t="n">
-        <v>3.287775328695732</v>
+        <v>3.2989816151179</v>
       </c>
     </row>
     <row r="1887">
@@ -44952,16 +44952,16 @@
         <v>3.164269284238807</v>
       </c>
       <c r="D1887" t="n">
-        <v>-2.227544772066536</v>
+        <v>-2.214808377119131</v>
       </c>
       <c r="E1887" t="n">
-        <v>2.272894951098445</v>
+        <v>2.277989509077407</v>
       </c>
       <c r="F1887" t="n">
-        <v>0.2033846959303053</v>
+        <v>0.2220618399672514</v>
       </c>
       <c r="G1887" t="n">
-        <v>3.28630010179699</v>
+        <v>3.297506388219158</v>
       </c>
     </row>
     <row r="1888">
@@ -44969,22 +44969,22 @@
         <v>45350</v>
       </c>
       <c r="B1888" t="n">
-        <v>3.691568158410714</v>
+        <v>3.691568158410715</v>
       </c>
       <c r="C1888" t="n">
         <v>3.179322694403679</v>
       </c>
       <c r="D1888" t="n">
-        <v>-2.030275366338537</v>
+        <v>-2.017538971391132</v>
       </c>
       <c r="E1888" t="n">
-        <v>2.366856123554517</v>
+        <v>2.371950681533479</v>
       </c>
       <c r="F1888" t="n">
-        <v>0.4006541016583035</v>
+        <v>0.4193312456952495</v>
       </c>
       <c r="G1888" t="n">
-        <v>3.419715155398661</v>
+        <v>3.430921441820829</v>
       </c>
     </row>
     <row r="1889">
@@ -44992,22 +44992,22 @@
         <v>45351</v>
       </c>
       <c r="B1889" t="n">
-        <v>3.676837974240574</v>
+        <v>3.676837974240575</v>
       </c>
       <c r="C1889" t="n">
         <v>3.166271560756996</v>
       </c>
       <c r="D1889" t="n">
-        <v>-1.831123259101438</v>
+        <v>-1.818386864154033</v>
       </c>
       <c r="E1889" t="n">
-        <v>2.433465832802673</v>
+        <v>2.438560390781635</v>
       </c>
       <c r="F1889" t="n">
-        <v>0.5659766276081168</v>
+        <v>0.5846537716450628</v>
       </c>
       <c r="G1889" t="n">
-        <v>3.505857537321866</v>
+        <v>3.517063823744034</v>
       </c>
     </row>
     <row r="1890">
@@ -45015,22 +45015,22 @@
         <v>45352</v>
       </c>
       <c r="B1890" t="n">
-        <v>3.685157806085277</v>
+        <v>3.685157806085278</v>
       </c>
       <c r="C1890" t="n">
         <v>3.175850633793205</v>
       </c>
       <c r="D1890" t="n">
-        <v>-1.605278106382027</v>
+        <v>-1.592541711434622</v>
       </c>
       <c r="E1890" t="n">
-        <v>2.533382966926646</v>
+        <v>2.538477524905608</v>
       </c>
       <c r="F1890" t="n">
-        <v>0.6079033031952805</v>
+        <v>0.6265804472322265</v>
       </c>
       <c r="G1890" t="n">
-        <v>3.540592615710373</v>
+        <v>3.551798902132541</v>
       </c>
     </row>
     <row r="1891">
@@ -45038,22 +45038,22 @@
         <v>45353</v>
       </c>
       <c r="B1891" t="n">
-        <v>3.684840248282099</v>
+        <v>3.6848402482821</v>
       </c>
       <c r="C1891" t="n">
         <v>3.176989778349264</v>
       </c>
       <c r="D1891" t="n">
-        <v>-1.319003294059333</v>
+        <v>-1.306266899111928</v>
       </c>
       <c r="E1891" t="n">
-        <v>2.649032036411783</v>
+        <v>2.654126594390745</v>
       </c>
       <c r="F1891" t="n">
-        <v>0.6079033031952805</v>
+        <v>0.6265804472322265</v>
       </c>
       <c r="G1891" t="n">
-        <v>3.541731760266432</v>
+        <v>3.5529380466886</v>
       </c>
     </row>
     <row r="1892">
@@ -45061,22 +45061,22 @@
         <v>45354</v>
       </c>
       <c r="B1892" t="n">
-        <v>3.710931958116214</v>
+        <v>3.710931958116216</v>
       </c>
       <c r="C1892" t="n">
         <v>3.179623552511371</v>
       </c>
       <c r="D1892" t="n">
-        <v>-1.092207466985999</v>
+        <v>-1.079471072038594</v>
       </c>
       <c r="E1892" t="n">
-        <v>2.742384141403224</v>
+        <v>2.747478699382186</v>
       </c>
       <c r="F1892" t="n">
-        <v>0.676017247816825</v>
+        <v>0.694694391853771</v>
       </c>
       <c r="G1892" t="n">
-        <v>3.585233901201466</v>
+        <v>3.596440187623634</v>
       </c>
     </row>
     <row r="1893">
@@ -45084,22 +45084,22 @@
         <v>45355</v>
       </c>
       <c r="B1893" t="n">
-        <v>3.768948099081566</v>
+        <v>3.768948099081568</v>
       </c>
       <c r="C1893" t="n">
         <v>3.185357256750008</v>
       </c>
       <c r="D1893" t="n">
-        <v>-0.80829873605725</v>
+        <v>-0.7955623411098451</v>
       </c>
       <c r="E1893" t="n">
-        <v>2.86168133801336</v>
+        <v>2.866775895992322</v>
       </c>
       <c r="F1893" t="n">
-        <v>0.676017247816825</v>
+        <v>0.694694391853771</v>
       </c>
       <c r="G1893" t="n">
-        <v>3.590967605440103</v>
+        <v>3.602173891862271</v>
       </c>
     </row>
     <row r="1894">
@@ -45107,22 +45107,22 @@
         <v>45356</v>
       </c>
       <c r="B1894" t="n">
-        <v>3.728574354425326</v>
+        <v>3.728574354425328</v>
       </c>
       <c r="C1894" t="n">
         <v>3.175619994356143</v>
       </c>
       <c r="D1894" t="n">
-        <v>-0.5613114858642979</v>
+        <v>-0.548575090916893</v>
       </c>
       <c r="E1894" t="n">
-        <v>2.950738975696676</v>
+        <v>2.955833533675638</v>
       </c>
       <c r="F1894" t="n">
-        <v>0.9230044980097771</v>
+        <v>0.9416816420467231</v>
       </c>
       <c r="G1894" t="n">
-        <v>3.729422693162009</v>
+        <v>3.740628979584177</v>
       </c>
     </row>
     <row r="1895">
@@ -45130,22 +45130,22 @@
         <v>45357</v>
       </c>
       <c r="B1895" t="n">
-        <v>3.747699084702411</v>
+        <v>3.747699084702413</v>
       </c>
       <c r="C1895" t="n">
         <v>3.165736513043235</v>
       </c>
       <c r="D1895" t="n">
-        <v>-0.2974746186602288</v>
+        <v>-0.284738223712824</v>
       </c>
       <c r="E1895" t="n">
-        <v>3.046390241265396</v>
+        <v>3.051484799244358</v>
       </c>
       <c r="F1895" t="n">
-        <v>0.9230044980097771</v>
+        <v>0.9416816420467231</v>
       </c>
       <c r="G1895" t="n">
-        <v>3.719539211849102</v>
+        <v>3.730745498271269</v>
       </c>
     </row>
     <row r="1896">
@@ -45153,22 +45153,22 @@
         <v>45358</v>
       </c>
       <c r="B1896" t="n">
-        <v>3.766313503906228</v>
+        <v>3.766313503906229</v>
       </c>
       <c r="C1896" t="n">
         <v>3.163901952543861</v>
       </c>
       <c r="D1896" t="n">
-        <v>-0.2976354476803584</v>
+        <v>-0.01749642284442698</v>
       </c>
       <c r="E1896" t="n">
-        <v>3.04449134915797</v>
+        <v>3.156546959092343</v>
       </c>
       <c r="F1896" t="n">
-        <v>0.9230044980097771</v>
+        <v>0.9416816420467231</v>
       </c>
       <c r="G1896" t="n">
-        <v>3.717704651349728</v>
+        <v>3.728910937771895</v>
       </c>
     </row>
     <row r="1897">
@@ -45176,19 +45176,19 @@
         <v>45359</v>
       </c>
       <c r="B1897" t="n">
-        <v>3.40760767729903</v>
+        <v>3.407607677299031</v>
       </c>
       <c r="C1897" t="n">
         <v>2.849409515865033</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.2976354476803584</v>
+        <v>-0.01749642284442698</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.04449134915797</v>
+        <v>3.156546959092343</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.9230044980097771</v>
+        <v>0.9416816420467231</v>
       </c>
       <c r="G1897" t="n">
         <v>2.842473312851401</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970907</v>
+        <v>3.304715716970906</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>

--- a/tame_output/ON/bt/strategyON_20240308.xlsx
+++ b/tame_output/ON/bt/strategyON_20240308.xlsx
@@ -758,17 +758,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>64.2%</t>
+          <t>76.6%</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>31.5%</t>
+          <t>28.4%</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>2.70</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -791,7 +791,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>36.7%</t>
+          <t>29.8%</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -801,35 +801,35 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>32.9%</t>
+          <t>15.5%</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
         <is>
-          <t>2024-03-04</t>
+          <t>2021-03-21</t>
         </is>
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2021-03-24</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>18</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>-31.7%</t>
+          <t>-11.3%</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>-3.5%</t>
+          <t>-2.7%</t>
         </is>
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>-2.2%</t>
+          <t>-1.8%</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -839,37 +839,37 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>-5.4%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="U3" t="inlineStr">
         <is>
-          <t>48.4%</t>
+          <t>63.8%</t>
         </is>
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>24.6%</t>
+          <t>22.7%</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.8</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.3</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>-4.0%</t>
+          <t>-5.1%</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
@@ -904,7 +904,7 @@
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>-26.7%</t>
+          <t>4.7%</t>
         </is>
       </c>
     </row>
@@ -916,17 +916,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>-23.4%</t>
+          <t>-19.8%</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>67.9%</t>
+          <t>68.9%</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.29</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -954,7 +954,7 @@
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>58.6%</t>
+          <t>60.7%</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -992,7 +992,7 @@
       </c>
       <c r="R4" t="inlineStr">
         <is>
-          <t>12.5%</t>
+          <t>13.2%</t>
         </is>
       </c>
       <c r="S4" t="inlineStr">
@@ -1007,17 +1007,17 @@
       </c>
       <c r="U4" t="inlineStr">
         <is>
-          <t>-13.2%</t>
+          <t>-6.5%</t>
         </is>
       </c>
       <c r="V4" t="inlineStr">
         <is>
-          <t>55.9%</t>
+          <t>56.3%</t>
         </is>
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-0.2</t>
+          <t>-0.1</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1027,7 +1027,7 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>469.9%</t>
+          <t>472.5%</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
@@ -1062,7 +1062,7 @@
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>-163.3%</t>
+          <t>-136.6%</t>
         </is>
       </c>
     </row>
@@ -1074,17 +1074,17 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>69.6%</t>
+          <t>73.0%</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>39.2%</t>
+          <t>39.5%</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>1.77</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -1112,7 +1112,7 @@
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>35.5%</t>
+          <t>36.0%</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="R5" t="inlineStr">
         <is>
-          <t>9.8%</t>
+          <t>10.0%</t>
         </is>
       </c>
       <c r="S5" t="inlineStr">
@@ -1165,17 +1165,17 @@
       </c>
       <c r="U5" t="inlineStr">
         <is>
-          <t>64.4%</t>
+          <t>69.4%</t>
         </is>
       </c>
       <c r="V5" t="inlineStr">
         <is>
-          <t>32.7%</t>
+          <t>33.0%</t>
         </is>
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>2.1</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -1185,7 +1185,7 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>-19.6%</t>
+          <t>-20.0%</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
@@ -1220,7 +1220,7 @@
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>-60.6%</t>
+          <t>-49.9%</t>
         </is>
       </c>
     </row>
@@ -1232,22 +1232,22 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>6.9%</t>
+          <t>8.5%</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>45.1%</t>
+          <t>45.2%</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>0.15</t>
+          <t>0.19</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>54.5%</t>
+          <t>54.6%</t>
         </is>
       </c>
       <c r="F6" t="n">
@@ -1270,7 +1270,7 @@
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>47.7%</t>
+          <t>48.1%</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1308,7 +1308,7 @@
       </c>
       <c r="R6" t="inlineStr">
         <is>
-          <t>6.8%</t>
+          <t>6.9%</t>
         </is>
       </c>
       <c r="S6" t="inlineStr">
@@ -1323,17 +1323,17 @@
       </c>
       <c r="U6" t="inlineStr">
         <is>
-          <t>15.6%</t>
+          <t>18.4%</t>
         </is>
       </c>
       <c r="V6" t="inlineStr">
         <is>
-          <t>37.2%</t>
+          <t>37.1%</t>
         </is>
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>0.5</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -1343,7 +1343,7 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>80.2%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
@@ -1378,7 +1378,7 @@
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>-129.8%</t>
+          <t>-121.6%</t>
         </is>
       </c>
     </row>
@@ -1390,22 +1390,22 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>24.5%</t>
+          <t>91.1%</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>55.0%</t>
+          <t>39.1%</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>0.45</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>59.3%</t>
+          <t>59.4%</t>
         </is>
       </c>
       <c r="F7" t="n">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>75.5%</t>
+          <t>45.0%</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>34.7%</t>
+          <t>34.8%</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>95.4%</t>
+          <t>78.9%</t>
         </is>
       </c>
       <c r="L7" t="inlineStr">
@@ -1443,11 +1443,11 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
-          <t>2024-03-08</t>
+          <t>2024-02-06</t>
         </is>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>23</v>
       </c>
       <c r="O7" t="inlineStr">
         <is>
@@ -1456,52 +1456,52 @@
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>-4.1%</t>
+          <t>-2.8%</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
         <is>
-          <t>-1.4%</t>
+          <t>-0.7%</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
         <is>
-          <t>9.5%</t>
+          <t>9.8%</t>
         </is>
       </c>
       <c r="S7" t="inlineStr">
         <is>
-          <t>-18.9%</t>
+          <t>-14.0%</t>
         </is>
       </c>
       <c r="T7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="U7" t="inlineStr">
         <is>
-          <t>18.8%</t>
+          <t>85.9%</t>
         </is>
       </c>
       <c r="V7" t="inlineStr">
         <is>
-          <t>44.9%</t>
+          <t>32.6%</t>
         </is>
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>0.4</t>
+          <t>2.6</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>0.2</t>
+          <t>0.1</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>-12.1%</t>
+          <t>-14.9%</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>-161.8%</t>
+          <t>-68.2%</t>
         </is>
       </c>
     </row>
@@ -44394,7 +44394,7 @@
         <v>45325</v>
       </c>
       <c r="B1863" t="n">
-        <v>3.304715716970906</v>
+        <v>3.304715716970907</v>
       </c>
       <c r="C1863" t="n">
         <v>3.116678975928913</v>
@@ -45179,19 +45179,19 @@
         <v>3.407607677299031</v>
       </c>
       <c r="C1897" t="n">
-        <v>2.849409515865033</v>
+        <v>3.1636016375704</v>
       </c>
       <c r="D1897" t="n">
-        <v>-0.01749642284442698</v>
+        <v>0.2496796276779079</v>
       </c>
       <c r="E1897" t="n">
-        <v>3.156546959092343</v>
+        <v>3.263117064327816</v>
       </c>
       <c r="F1897" t="n">
-        <v>0.9416816420467231</v>
+        <v>1.024183251834231</v>
       </c>
       <c r="G1897" t="n">
-        <v>2.842473312851401</v>
+        <v>3.778111588670939</v>
       </c>
     </row>
   </sheetData>
